--- a/news_daily/2026-09-14.xlsx
+++ b/news_daily/2026-09-14.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BH$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BH$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BH$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BH$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH5"/>
+  <dimension ref="A1:BL5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -510,6 +510,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -813,6 +817,26 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -863,13 +887,17 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -918,7 +946,11 @@
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>14be0378651e4370a477f2b967b01548</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>09d8b15e885b0d8e31785130</t>
@@ -939,7 +971,11 @@
       <c r="AL2" s="2" t="inlineStr"/>
       <c r="AM2" s="2" t="inlineStr"/>
       <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr"/>
+      <c r="AO2" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP2" s="2" t="inlineStr"/>
       <c r="AQ2" s="2" t="inlineStr"/>
       <c r="AR2" s="2" t="inlineStr"/>
@@ -983,6 +1019,18 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1018,28 +1066,32 @@
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>股價下跌</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -1079,7 +1131,7 @@
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>PRICE_MOVEMENT</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
@@ -1088,7 +1140,11 @@
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr"/>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>61418680f9d645bc834c9bd6f7bd0cfa</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
           <t>6daefbdcff9ce3b2642325fd</t>
@@ -1109,7 +1165,11 @@
       <c r="AL3" s="2" t="inlineStr"/>
       <c r="AM3" s="2" t="inlineStr"/>
       <c r="AN3" s="2" t="inlineStr"/>
-      <c r="AO3" s="2" t="inlineStr"/>
+      <c r="AO3" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP3" s="2" t="inlineStr"/>
       <c r="AQ3" s="2" t="inlineStr"/>
       <c r="AR3" s="2" t="inlineStr"/>
@@ -1145,6 +1205,22 @@
         </is>
       </c>
       <c r="BH3" s="2" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1180,28 +1256,32 @@
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -1241,7 +1321,7 @@
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -1250,7 +1330,11 @@
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr"/>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>226a975b92f54724b74b75b88f9a08a8</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
           <t>bc4d92071d47e0bb5b828e9d</t>
@@ -1271,7 +1355,11 @@
       <c r="AL4" s="2" t="inlineStr"/>
       <c r="AM4" s="2" t="inlineStr"/>
       <c r="AN4" s="2" t="inlineStr"/>
-      <c r="AO4" s="2" t="inlineStr"/>
+      <c r="AO4" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP4" s="2" t="inlineStr"/>
       <c r="AQ4" s="2" t="inlineStr"/>
       <c r="AR4" s="2" t="inlineStr"/>
@@ -1315,6 +1403,22 @@
         </is>
       </c>
       <c r="BH4" s="2" t="inlineStr"/>
+      <c r="BI4" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ4" s="2" t="inlineStr"/>
+      <c r="BK4" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1365,13 +1469,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1420,7 +1528,11 @@
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr"/>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>d21143d9296d4b03a8d6407dc64186f9</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
           <t>ca109fa17a073b927758f11c</t>
@@ -1441,7 +1553,11 @@
       <c r="AL5" s="2" t="inlineStr"/>
       <c r="AM5" s="2" t="inlineStr"/>
       <c r="AN5" s="2" t="inlineStr"/>
-      <c r="AO5" s="2" t="inlineStr"/>
+      <c r="AO5" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP5" s="2" t="inlineStr"/>
       <c r="AQ5" s="2" t="inlineStr"/>
       <c r="AR5" s="2" t="inlineStr"/>
@@ -1485,9 +1601,21 @@
         </is>
       </c>
       <c r="BH5" s="2" t="inlineStr"/>
+      <c r="BI5" s="2" t="inlineStr"/>
+      <c r="BJ5" s="2" t="inlineStr"/>
+      <c r="BK5" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH5"/>
+  <autoFilter ref="A1:BL5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1498,7 +1626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1561,6 +1689,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1864,9 +1996,29 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH1"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1877,7 +2029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1940,6 +2092,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2243,9 +2399,29 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH1"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2256,7 +2432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2319,6 +2495,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2622,9 +2802,29 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH1"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2635,7 +2835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA5"/>
+  <dimension ref="A1:AA8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2685,134 +2885,134 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>methods</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>started_at</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>finished_at</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>llm_calls</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>cache_reused</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>selected_company_count</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>collected</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>rows</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>errors</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>stages</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>quota_reserved</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>重複合併</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>sources</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>rows</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>changed</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>missing_publication_time</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>ticker_statuses</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>llm_calls</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>start</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>methods</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>cache_reused</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>major</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>selected_company_count</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>collected</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>errors</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>stages</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>quota_reserved</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>重複合併</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ticker-audit-20261024-081549</t>
+          <t>daily-2026-10-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>ticker-audit</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -2822,46 +3022,80 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T08:15:49.296780+08:00</t>
+          <t>2026-10-25T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T08:15:49.296790+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>1691</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>257</v>
-      </c>
-      <c r="I2" s="2" t="n">
+          <t>2026-10-26T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:23:38.366332+08:00</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:40:53.776257+08:00</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr"/>
-      <c r="U2" s="2" t="inlineStr"/>
-      <c r="V2" s="2" t="inlineStr"/>
-      <c r="W2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="n">
+        <v>1926</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>1976</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>1961</v>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 16 筆', '方法二 1958 筆；公司 503 家（非輪替）', '市場事件搜尋 2 筆', 'FinBERT 完成 1976 筆']</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>1961</v>
+      </c>
+      <c r="W2" s="2" t="n">
+        <v>15</v>
+      </c>
       <c r="X2" s="2" t="inlineStr"/>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -2870,12 +3104,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+          <t>daily-2026-10-25</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -2885,90 +3119,94 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:26:34.299718+08:00</t>
+          <t>2026-10-24T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:32:11.776786+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
+          <t>2026-10-25T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:23:17.137147+08:00</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:40:12.120180+08:00</t>
+        </is>
+      </c>
       <c r="K3" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>2032</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>503</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>34</v>
+        <v>2089</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="T3" s="2" t="n">
-        <v>17</v>
+        <v>2067</v>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 26 筆', '方法二 2059 筆；公司 503 家（非輪替）', '市場事件搜尋 6 筆', 'FinBERT 完成 2089 筆']</t>
+        </is>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X3" s="2" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
-      </c>
-      <c r="Y3" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="Z3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>2067</v>
+      </c>
+      <c r="W3" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="X3" s="2" t="inlineStr"/>
+      <c r="Y3" s="2" t="inlineStr"/>
+      <c r="Z3" s="2" t="inlineStr"/>
+      <c r="AA3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+          <t>daily-2026-10-24</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -2978,94 +3216,94 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:20:47.845317+08:00</t>
+          <t>2026-10-23T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:21:20.302846+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
+          <t>2026-10-24T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:44:09.884829+08:00</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T13:04:34.984103+08:00</t>
+        </is>
+      </c>
       <c r="K4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>3760</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>503</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>2</v>
+        <v>3802</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" s="2" t="n">
-        <v>2</v>
+        <v>3825</v>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 158 筆', '方法二 3638 筆；公司 503 家（非輪替）', '市場事件搜尋 8 筆', 'FinBERT 完成 3802 筆']</t>
+        </is>
       </c>
       <c r="U4" s="2" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X4" s="2" t="inlineStr">
-        <is>
-          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
-        </is>
-      </c>
-      <c r="Y4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA4" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>3793</v>
+      </c>
+      <c r="W4" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="X4" s="2" t="inlineStr"/>
+      <c r="Y4" s="2" t="inlineStr"/>
+      <c r="Z4" s="2" t="inlineStr"/>
+      <c r="AA4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>ticker-audit-20261024-081549</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>ticker-audit</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -3073,89 +3311,342 @@
           <t>success</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:19:11.949238+08:00</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:19:18.833437+08:00</t>
-        </is>
-      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="n">
-        <v>33</v>
-      </c>
+      <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296780+08:00</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296790+08:00</t>
+        </is>
+      </c>
       <c r="K5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="2" t="n">
-        <v>33</v>
-      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
       <c r="R5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="T5" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="U5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X5" s="2" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
+        <v>1691</v>
+      </c>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="n">
+        <v>19</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>1</v>
+        <v>257</v>
       </c>
       <c r="Z5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA5" s="2" t="n">
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:34.299718+08:00</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:32:11.776786+08:00</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="M6" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N6" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="2" t="inlineStr"/>
+      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:20:47.845317+08:00</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:21:20.302846+08:00</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="W7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="2" t="inlineStr"/>
+      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="Z7" s="2" t="inlineStr"/>
+      <c r="AA7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:11.949238+08:00</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:18.833437+08:00</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="2" t="inlineStr"/>
+      <c r="Y8" s="2" t="inlineStr"/>
+      <c r="Z8" s="2" t="inlineStr"/>
+      <c r="AA8" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA5"/>
+  <autoFilter ref="A1:AA8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>